--- a/docs/Mapping_casi_uso/morte/Morte_004.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_004.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="120">
   <si>
     <t>Sezione</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
   </si>
   <si>
     <t>Luogo</t>
@@ -424,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -1062,7 +1068,7 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>14</v>
@@ -1071,7 +1077,7 @@
         <v>52</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1085,7 +1091,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>14</v>
@@ -1197,19 +1203,19 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1220,10 +1226,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
@@ -1232,7 +1238,7 @@
         <v>26</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1243,53 +1249,53 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>90</v>
@@ -1298,7 +1304,7 @@
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>91</v>
@@ -1307,12 +1313,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>92</v>
@@ -1321,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>93</v>
@@ -1330,12 +1336,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>94</v>
@@ -1344,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>95</v>
@@ -1353,12 +1359,12 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>96</v>
@@ -1367,7 +1373,7 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>97</v>
@@ -1376,12 +1382,12 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>98</v>
@@ -1390,44 +1396,44 @@
         <v>14</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>101</v>
@@ -1436,44 +1442,44 @@
         <v>14</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>104</v>
@@ -1482,7 +1488,7 @@
         <v>14</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>105</v>
@@ -1491,12 +1497,12 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>106</v>
@@ -1505,7 +1511,7 @@
         <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>107</v>
@@ -1514,12 +1520,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>108</v>
@@ -1528,7 +1534,7 @@
         <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>109</v>
@@ -1537,44 +1543,44 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>115</v>
@@ -1588,7 +1594,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>116</v>
@@ -1597,7 +1603,7 @@
         <v>14</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>117</v>
@@ -1606,6 +1612,29 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/morte/Morte_004.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_004.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="118">
   <si>
     <t>Sezione</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>191</t>
-  </si>
-  <si>
     <t>197</t>
   </si>
   <si>
@@ -89,178 +86,175 @@
     <t>nomeEnte</t>
   </si>
   <si>
-    <t>Data richiesta</t>
+    <t>Provincia ente</t>
+  </si>
+  <si>
+    <t>idProvinciaEnte</t>
+  </si>
+  <si>
+    <t>Provincia ente - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaEnte</t>
+  </si>
+  <si>
+    <t>Comune ente</t>
+  </si>
+  <si>
+    <t>idComuneEnte</t>
+  </si>
+  <si>
+    <t>Comune ente - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneEnte</t>
+  </si>
+  <si>
+    <t>Stato ente</t>
+  </si>
+  <si>
+    <t>nazioneEnte</t>
+  </si>
+  <si>
+    <t>Stato - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeNazioneEnte</t>
+  </si>
+  <si>
+    <t>Formazione atto</t>
+  </si>
+  <si>
+    <t>Numero comunale</t>
+  </si>
+  <si>
+    <t>evento</t>
+  </si>
+  <si>
+    <t>numeroatto</t>
+  </si>
+  <si>
+    <t>Data formazione</t>
+  </si>
+  <si>
+    <t>dataformazione</t>
+  </si>
+  <si>
+    <t>Ora formazione</t>
+  </si>
+  <si>
+    <t>ora</t>
+  </si>
+  <si>
+    <t>Minuti formazione</t>
+  </si>
+  <si>
+    <t>minuto</t>
+  </si>
+  <si>
+    <t>Dati decesso</t>
+  </si>
+  <si>
+    <t>Data morte</t>
+  </si>
+  <si>
+    <t>evento.datiDiMorte</t>
+  </si>
+  <si>
+    <t>dataMorte</t>
+  </si>
+  <si>
+    <t>Ora</t>
+  </si>
+  <si>
+    <t>oraMorte</t>
+  </si>
+  <si>
+    <t>Minuti</t>
+  </si>
+  <si>
+    <t>minutoMorte</t>
+  </si>
+  <si>
+    <t>Data presunta inizio</t>
+  </si>
+  <si>
+    <t>dataPresuntaMorteDa</t>
+  </si>
+  <si>
+    <t>Data presunta fine</t>
+  </si>
+  <si>
+    <t>dataPresuntaMorteA</t>
+  </si>
+  <si>
+    <t>Note data e ora presunta</t>
+  </si>
+  <si>
+    <t>testoDataPresuntaMorte</t>
+  </si>
+  <si>
+    <t>Data rinvenimento cadavere</t>
+  </si>
+  <si>
+    <t>dataRinvenimentoCadavere</t>
+  </si>
+  <si>
+    <t>Luogo</t>
+  </si>
+  <si>
+    <t>luogoMorte</t>
+  </si>
+  <si>
+    <t>Stato</t>
+  </si>
+  <si>
+    <t>idStatoMorte</t>
+  </si>
+  <si>
+    <t>nomeStatoMorte</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>idProvinciaMorte</t>
+  </si>
+  <si>
+    <t>Provincia - Descrizione</t>
+  </si>
+  <si>
+    <t>siglaProvinciaMorte</t>
+  </si>
+  <si>
+    <t>Comune</t>
+  </si>
+  <si>
+    <t>idComuneMorte</t>
+  </si>
+  <si>
+    <t>Comune - Descrizione</t>
+  </si>
+  <si>
+    <t>nomeComuneMorte</t>
+  </si>
+  <si>
+    <t>Indirizzo</t>
+  </si>
+  <si>
+    <t>indirizzoMorte</t>
+  </si>
+  <si>
+    <t>Dati della trascrizione</t>
+  </si>
+  <si>
+    <t>Data richiesta trascrizione</t>
   </si>
   <si>
     <t>evento.trascrizioneMorte</t>
   </si>
   <si>
     <t>dataComunicazione</t>
-  </si>
-  <si>
-    <t>Provincia ente</t>
-  </si>
-  <si>
-    <t>idProvinciaEnte</t>
-  </si>
-  <si>
-    <t>Provincia ente - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaEnte</t>
-  </si>
-  <si>
-    <t>Comune ente</t>
-  </si>
-  <si>
-    <t>idComuneEnte</t>
-  </si>
-  <si>
-    <t>Comune ente - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneEnte</t>
-  </si>
-  <si>
-    <t>Stato ente</t>
-  </si>
-  <si>
-    <t>nazioneEnte</t>
-  </si>
-  <si>
-    <t>Stato - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeNazioneEnte</t>
-  </si>
-  <si>
-    <t>Formazione atto</t>
-  </si>
-  <si>
-    <t>Numero comunale</t>
-  </si>
-  <si>
-    <t>evento</t>
-  </si>
-  <si>
-    <t>numeroatto</t>
-  </si>
-  <si>
-    <t>Data formazione</t>
-  </si>
-  <si>
-    <t>dataformazione</t>
-  </si>
-  <si>
-    <t>Ora formazione</t>
-  </si>
-  <si>
-    <t>ora</t>
-  </si>
-  <si>
-    <t>Minuti formazione</t>
-  </si>
-  <si>
-    <t>minuto</t>
-  </si>
-  <si>
-    <t>Dati decesso</t>
-  </si>
-  <si>
-    <t>Data morte</t>
-  </si>
-  <si>
-    <t>evento.datiDiMorte</t>
-  </si>
-  <si>
-    <t>dataMorte</t>
-  </si>
-  <si>
-    <t>Ora</t>
-  </si>
-  <si>
-    <t>oraMorte</t>
-  </si>
-  <si>
-    <t>Minuti</t>
-  </si>
-  <si>
-    <t>minutoMorte</t>
-  </si>
-  <si>
-    <t>Data presunta inizio</t>
-  </si>
-  <si>
-    <t>dataPresuntaMorteDa</t>
-  </si>
-  <si>
-    <t>Data presunta fine</t>
-  </si>
-  <si>
-    <t>dataPresuntaMorteA</t>
-  </si>
-  <si>
-    <t>Note data e ora presunta</t>
-  </si>
-  <si>
-    <t>testoDataPresuntaMorte</t>
-  </si>
-  <si>
-    <t>Data rinvenimento cadavere</t>
-  </si>
-  <si>
-    <t>dataRinvenimentoCadavere</t>
-  </si>
-  <si>
-    <t>Luogo</t>
-  </si>
-  <si>
-    <t>luogoMorte</t>
-  </si>
-  <si>
-    <t>Stato</t>
-  </si>
-  <si>
-    <t>idStatoMorte</t>
-  </si>
-  <si>
-    <t>nomeStatoMorte</t>
-  </si>
-  <si>
-    <t>Provincia</t>
-  </si>
-  <si>
-    <t>idProvinciaMorte</t>
-  </si>
-  <si>
-    <t>Provincia - Descrizione</t>
-  </si>
-  <si>
-    <t>siglaProvinciaMorte</t>
-  </si>
-  <si>
-    <t>Comune</t>
-  </si>
-  <si>
-    <t>idComuneMorte</t>
-  </si>
-  <si>
-    <t>Comune - Descrizione</t>
-  </si>
-  <si>
-    <t>nomeComuneMorte</t>
-  </si>
-  <si>
-    <t>Indirizzo</t>
-  </si>
-  <si>
-    <t>indirizzoMorte</t>
-  </si>
-  <si>
-    <t>Dati della trascrizione</t>
-  </si>
-  <si>
-    <t>Data richiesta trascrizione</t>
   </si>
   <si>
     <t>Riassunto</t>
@@ -430,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="26.12890625" customWidth="true" bestFit="true"/>
@@ -496,148 +490,148 @@
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>27</v>
@@ -646,21 +640,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>29</v>
@@ -669,44 +663,44 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -715,90 +709,90 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>43</v>
@@ -807,12 +801,12 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>44</v>
@@ -821,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>45</v>
@@ -830,67 +824,67 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>53</v>
@@ -899,21 +893,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
@@ -922,21 +916,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>57</v>
@@ -945,21 +939,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>59</v>
@@ -968,21 +962,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -991,21 +985,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1014,21 +1008,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1037,67 +1031,67 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1106,21 +1100,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1129,21 +1123,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1152,21 +1146,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1175,467 +1169,421 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
